--- a/data-collection/Manawatu GymSports WAG Opens 2025.xlsx
+++ b/data-collection/Manawatu GymSports WAG Opens 2025.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3855,7 +3855,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15361,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16263,7 +16263,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17054,7 +17054,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17845,7 +17845,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18804,7 +18804,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19026,7 +19026,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19137,7 +19137,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19248,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19650,7 +19650,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -19761,7 +19761,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -20387,7 +20387,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -20498,7 +20498,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -20900,7 +20900,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21011,7 +21011,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21122,7 +21122,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21455,7 +21455,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21566,7 +21566,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21677,7 +21677,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21788,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -21899,7 +21899,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22010,7 +22010,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22121,7 +22121,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22565,7 +22565,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22676,7 +22676,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22898,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23231,7 +23231,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23342,7 +23342,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23453,7 +23453,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23564,7 +23564,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23675,7 +23675,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -23897,7 +23897,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24119,7 +24119,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24785,7 +24785,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -24896,7 +24896,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25229,7 +25229,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25451,7 +25451,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25562,7 +25562,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25673,7 +25673,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25784,7 +25784,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26117,7 +26117,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26228,7 +26228,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26339,7 +26339,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26450,7 +26450,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26672,7 +26672,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26783,7 +26783,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -26963,7 +26963,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27189,7 +27189,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27528,7 +27528,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27867,7 +27867,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -27980,7 +27980,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28093,7 +28093,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28317,7 +28317,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28880,7 +28880,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -28993,7 +28993,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29106,7 +29106,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29219,7 +29219,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29332,7 +29332,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29445,7 +29445,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29671,7 +29671,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30010,7 +30010,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30123,7 +30123,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30236,7 +30236,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30462,7 +30462,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30688,7 +30688,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30801,7 +30801,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31207,7 +31207,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31320,7 +31320,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31433,7 +31433,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31659,7 +31659,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31772,7 +31772,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31885,7 +31885,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -31998,7 +31998,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32111,7 +32111,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32335,7 +32335,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32448,7 +32448,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32561,7 +32561,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32672,7 +32672,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32785,7 +32785,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -32896,7 +32896,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33122,7 +33122,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33461,7 +33461,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33574,7 +33574,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33687,7 +33687,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33800,7 +33800,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -33913,7 +33913,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34026,7 +34026,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34139,7 +34139,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34252,7 +34252,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34365,7 +34365,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34478,7 +34478,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34591,7 +34591,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34704,7 +34704,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34817,7 +34817,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -34930,7 +34930,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35043,7 +35043,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35156,7 +35156,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35336,7 +35336,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -35447,7 +35447,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35669,7 +35669,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35780,7 +35780,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -35891,7 +35891,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36002,7 +36002,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36113,7 +36113,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36224,7 +36224,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36335,7 +36335,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36446,7 +36446,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36557,7 +36557,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36668,7 +36668,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -36848,7 +36848,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -36959,7 +36959,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37070,7 +37070,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37181,7 +37181,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37292,7 +37292,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37403,7 +37403,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37514,7 +37514,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37625,7 +37625,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37847,7 +37847,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -37958,7 +37958,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38069,7 +38069,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38180,7 +38180,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38291,7 +38291,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38402,7 +38402,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38513,7 +38513,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38624,7 +38624,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38846,7 +38846,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -38957,7 +38957,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39068,7 +39068,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39179,7 +39179,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39290,7 +39290,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39401,7 +39401,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39512,7 +39512,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39623,7 +39623,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39734,7 +39734,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39845,7 +39845,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -39956,7 +39956,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40067,7 +40067,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40178,7 +40178,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40289,7 +40289,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40400,7 +40400,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40622,7 +40622,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40733,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -40913,7 +40913,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -41024,7 +41024,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41135,7 +41135,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41246,7 +41246,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41357,7 +41357,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41537,7 +41537,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41763,7 +41763,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -41943,7 +41943,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -42054,7 +42054,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42165,7 +42165,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42387,7 +42387,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42498,7 +42498,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42720,7 +42720,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42831,7 +42831,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43053,7 +43053,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43164,7 +43164,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43275,7 +43275,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43386,7 +43386,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43497,7 +43497,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43608,7 +43608,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43719,7 +43719,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43830,7 +43830,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -43941,7 +43941,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44052,7 +44052,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44163,7 +44163,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44274,7 +44274,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44385,7 +44385,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44496,7 +44496,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44607,7 +44607,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44718,7 +44718,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44829,7 +44829,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -44940,7 +44940,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45051,7 +45051,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45162,7 +45162,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45273,7 +45273,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45384,7 +45384,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45495,7 +45495,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45606,7 +45606,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45717,7 +45717,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -45828,7 +45828,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46008,7 +46008,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -46119,7 +46119,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46230,7 +46230,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46341,7 +46341,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46452,7 +46452,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46563,7 +46563,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46674,7 +46674,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46785,7 +46785,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -46896,7 +46896,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47007,7 +47007,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47118,7 +47118,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47229,7 +47229,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47340,7 +47340,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47451,7 +47451,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47562,7 +47562,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47673,7 +47673,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47784,7 +47784,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -47895,7 +47895,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48006,7 +48006,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48117,7 +48117,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48228,7 +48228,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48339,7 +48339,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48450,7 +48450,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48561,7 +48561,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48672,7 +48672,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48783,7 +48783,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -48894,7 +48894,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49005,7 +49005,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49116,7 +49116,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49227,7 +49227,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49338,7 +49338,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49449,7 +49449,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49560,7 +49560,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49671,7 +49671,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49782,7 +49782,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -49893,7 +49893,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50004,7 +50004,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50115,7 +50115,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50226,7 +50226,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50337,7 +50337,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50448,7 +50448,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50670,7 +50670,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -50892,7 +50892,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51003,7 +51003,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51114,7 +51114,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51225,7 +51225,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51405,7 +51405,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -51516,7 +51516,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51627,7 +51627,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51738,7 +51738,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51849,7 +51849,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -51960,7 +51960,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52071,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52182,7 +52182,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52404,7 +52404,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52515,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52626,7 +52626,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52737,7 +52737,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52848,7 +52848,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -52959,7 +52959,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53070,7 +53070,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53181,7 +53181,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53292,7 +53292,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53403,7 +53403,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53514,7 +53514,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53625,7 +53625,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53736,7 +53736,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53847,7 +53847,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -53958,7 +53958,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54069,7 +54069,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54180,7 +54180,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54291,7 +54291,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54402,7 +54402,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54513,7 +54513,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54624,7 +54624,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54735,7 +54735,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54846,7 +54846,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -54957,7 +54957,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55068,7 +55068,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -55359,7 +55359,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55470,7 +55470,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55581,7 +55581,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55692,7 +55692,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55803,7 +55803,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -55914,7 +55914,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56025,7 +56025,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56136,7 +56136,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56247,7 +56247,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56358,7 +56358,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56469,7 +56469,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56580,7 +56580,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56691,7 +56691,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56802,7 +56802,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -56913,7 +56913,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57024,7 +57024,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57135,7 +57135,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57246,7 +57246,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57357,7 +57357,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57468,7 +57468,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57579,7 +57579,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57690,7 +57690,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57801,7 +57801,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -57912,7 +57912,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58023,7 +58023,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58134,7 +58134,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58245,7 +58245,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58356,7 +58356,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58467,7 +58467,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58578,7 +58578,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58689,7 +58689,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58800,7 +58800,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -58911,7 +58911,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59022,7 +59022,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59133,7 +59133,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59244,7 +59244,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59355,7 +59355,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59466,7 +59466,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59577,7 +59577,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59757,7 +59757,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -59868,7 +59868,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -59979,7 +59979,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60090,7 +60090,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60201,7 +60201,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60312,7 +60312,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60423,7 +60423,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60534,7 +60534,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60645,7 +60645,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60756,7 +60756,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60867,7 +60867,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -60978,7 +60978,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61089,7 +61089,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61200,7 +61200,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61311,7 +61311,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61422,7 +61422,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61533,7 +61533,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61644,7 +61644,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61755,7 +61755,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61866,7 +61866,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -61977,7 +61977,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62088,7 +62088,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62199,7 +62199,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62310,7 +62310,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62421,7 +62421,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62532,7 +62532,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62643,7 +62643,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62754,7 +62754,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62865,7 +62865,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -62976,7 +62976,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63087,7 +63087,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63198,7 +63198,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63309,7 +63309,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63420,7 +63420,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63531,7 +63531,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63642,7 +63642,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63753,7 +63753,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63864,7 +63864,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -63975,7 +63975,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64155,7 +64155,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -64266,7 +64266,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64377,7 +64377,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64488,7 +64488,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64599,7 +64599,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64710,7 +64710,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64821,7 +64821,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -64932,7 +64932,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65043,7 +65043,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65154,7 +65154,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65265,7 +65265,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65376,7 +65376,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65487,7 +65487,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65598,7 +65598,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65709,7 +65709,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65820,7 +65820,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -65931,7 +65931,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66042,7 +66042,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66153,7 +66153,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66264,7 +66264,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66375,7 +66375,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66486,7 +66486,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66597,7 +66597,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66708,7 +66708,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66819,7 +66819,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -66930,7 +66930,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67041,7 +67041,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67152,7 +67152,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67263,7 +67263,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67374,7 +67374,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67485,7 +67485,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67596,7 +67596,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67707,7 +67707,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -67887,7 +67887,7 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>comp-end-date</t>
+          <t>comp-start-date</t>
         </is>
       </c>
     </row>
@@ -67998,7 +67998,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68109,7 +68109,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68220,7 +68220,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68331,7 +68331,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68442,7 +68442,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68553,7 +68553,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68664,7 +68664,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68775,7 +68775,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68886,7 +68886,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -68997,7 +68997,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69108,7 +69108,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69219,7 +69219,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69330,7 +69330,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69441,7 +69441,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69552,7 +69552,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69663,7 +69663,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69774,7 +69774,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69885,7 +69885,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -69996,7 +69996,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -70107,7 +70107,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -70218,7 +70218,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -70329,7 +70329,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -70440,7 +70440,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
@@ -70551,7 +70551,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-05-31</t>
         </is>
       </c>
     </row>
